--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest without electricity.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest without electricity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20402"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Raw data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9185937C-A6BC-4128-BB0F-ACC0A8102AE0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15AC727-938F-BE46-9E40-CB4D8E2191C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="504" windowWidth="28800" windowHeight="17496" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -23,12 +23,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1908" uniqueCount="247">
   <si>
     <t>Activity</t>
   </si>
@@ -160,9 +171,6 @@
   </si>
   <si>
     <t>electricity, high voltage</t>
-  </si>
-  <si>
-    <t>World</t>
   </si>
   <si>
     <t>Database</t>
@@ -852,7 +860,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -915,7 +923,6 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1232,21 +1239,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:K310"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="70.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.6640625" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B1" s="10" t="s">
         <v>16</v>
@@ -1258,7 +1265,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1268,12 +1275,12 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -1282,12 +1289,12 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -1296,7 +1303,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1310,7 +1317,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1324,12 +1331,12 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -1338,7 +1345,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1352,7 +1359,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1364,7 +1371,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1390,9 +1397,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="9">
         <v>1</v>
@@ -1411,12 +1418,12 @@
         <v>17</v>
       </c>
       <c r="H11" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="9">
         <v>1</v>
@@ -1435,12 +1442,12 @@
         <v>20</v>
       </c>
       <c r="H12" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>55</v>
       </c>
       <c r="B13" s="4">
         <v>1.94</v>
@@ -1449,7 +1456,7 @@
         <v>18</v>
       </c>
       <c r="D13" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E13" t="s">
         <v>24</v>
@@ -1461,7 +1468,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1471,12 +1478,12 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -1485,12 +1492,12 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -1499,7 +1506,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1513,7 +1520,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1527,12 +1534,12 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -1541,7 +1548,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1555,7 +1562,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1567,7 +1574,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1593,9 +1600,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B23" s="9">
         <v>1</v>
@@ -1614,12 +1621,12 @@
         <v>17</v>
       </c>
       <c r="H23" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B24" s="9">
         <v>0.1</v>
@@ -1638,12 +1645,12 @@
         <v>20</v>
       </c>
       <c r="H24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
         <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>60</v>
       </c>
       <c r="B25" s="4">
         <v>0.1</v>
@@ -1661,12 +1668,12 @@
         <v>20</v>
       </c>
       <c r="H25" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>62</v>
       </c>
       <c r="B26" s="4">
         <v>0.8</v>
@@ -1684,12 +1691,12 @@
         <v>20</v>
       </c>
       <c r="H26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B27" s="4">
         <v>0.38800000000000001</v>
@@ -1698,7 +1705,7 @@
         <v>18</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E27" t="s">
         <v>24</v>
@@ -1710,7 +1717,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1720,12 +1727,12 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -1734,12 +1741,12 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -1748,7 +1755,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1762,7 +1769,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1776,12 +1783,12 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -1790,7 +1797,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1804,7 +1811,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1816,7 +1823,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1842,9 +1849,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B37" s="9">
         <v>1</v>
@@ -1863,12 +1870,12 @@
         <v>17</v>
       </c>
       <c r="H37" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B38" s="9">
         <v>0.879</v>
@@ -1887,12 +1894,12 @@
         <v>20</v>
       </c>
       <c r="H38" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
         <v>66</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>67</v>
       </c>
       <c r="B39" s="4">
         <v>2.3999999999999998E-3</v>
@@ -1910,12 +1917,12 @@
         <v>20</v>
       </c>
       <c r="H39" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" t="s">
-        <v>69</v>
       </c>
       <c r="B40" s="4">
         <v>0.11799999999999999</v>
@@ -1933,12 +1940,12 @@
         <v>20</v>
       </c>
       <c r="H40" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B41" s="4">
         <v>1.94</v>
@@ -1947,7 +1954,7 @@
         <v>18</v>
       </c>
       <c r="D41" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E41" t="s">
         <v>24</v>
@@ -1959,7 +1966,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1969,12 +1976,12 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -1983,12 +1990,12 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C44" s="8"/>
       <c r="D44" s="8"/>
@@ -1997,7 +2004,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -2011,7 +2018,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2025,12 +2032,12 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B47" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C47" s="8"/>
       <c r="D47" s="8"/>
@@ -2039,7 +2046,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -2053,7 +2060,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2065,7 +2072,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2091,9 +2098,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B51" s="9">
         <v>1</v>
@@ -2112,12 +2119,12 @@
         <v>17</v>
       </c>
       <c r="H51" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B52" s="9">
         <v>0.435</v>
@@ -2136,12 +2143,12 @@
         <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" s="4">
         <v>0.32500000000000001</v>
@@ -2159,12 +2166,12 @@
         <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B54" s="4">
         <v>0.24</v>
@@ -2182,12 +2189,12 @@
         <v>20</v>
       </c>
       <c r="H54" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55" s="4">
         <v>1.48</v>
@@ -2196,7 +2203,7 @@
         <v>18</v>
       </c>
       <c r="D55" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E55" t="s">
         <v>24</v>
@@ -2208,7 +2215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2218,12 +2225,12 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C57" s="8"/>
       <c r="D57" s="8"/>
@@ -2232,12 +2239,12 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C58" s="8"/>
       <c r="D58" s="8"/>
@@ -2246,7 +2253,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2260,7 +2267,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2274,12 +2281,12 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B61" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C61" s="8"/>
       <c r="D61" s="8"/>
@@ -2288,7 +2295,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2302,7 +2309,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2314,7 +2321,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2340,9 +2347,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B65" s="9">
         <v>1</v>
@@ -2361,12 +2368,12 @@
         <v>17</v>
       </c>
       <c r="H65" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B66" s="9">
         <v>0.25</v>
@@ -2388,9 +2395,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B67" s="4">
         <v>0.75</v>
@@ -2408,12 +2415,12 @@
         <v>20</v>
       </c>
       <c r="H67" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B68" s="4">
         <v>0.48499999999999999</v>
@@ -2422,7 +2429,7 @@
         <v>18</v>
       </c>
       <c r="D68" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E68" t="s">
         <v>24</v>
@@ -2434,7 +2441,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2444,12 +2451,12 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C70" s="8"/>
       <c r="D70" s="8"/>
@@ -2458,12 +2465,12 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B71" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C71" s="8"/>
       <c r="D71" s="8"/>
@@ -2472,7 +2479,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2486,7 +2493,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2500,12 +2507,12 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B74" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C74" s="8"/>
       <c r="D74" s="8"/>
@@ -2514,7 +2521,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2528,7 +2535,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2540,7 +2547,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2566,9 +2573,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78" s="9">
         <v>1</v>
@@ -2587,12 +2594,12 @@
         <v>17</v>
       </c>
       <c r="H78" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B79" s="9">
         <v>0.97099999999999997</v>
@@ -2611,12 +2618,12 @@
         <v>20</v>
       </c>
       <c r="H79" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80" s="9">
         <v>0.03</v>
@@ -2635,12 +2642,12 @@
         <v>20</v>
       </c>
       <c r="H80" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B81" s="4">
         <v>5.2499999999999998E-2</v>
@@ -2658,12 +2665,12 @@
         <v>20</v>
       </c>
       <c r="H81" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B82" s="4">
         <v>1.78</v>
@@ -2672,7 +2679,7 @@
         <v>18</v>
       </c>
       <c r="D82" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E82" t="s">
         <v>24</v>
@@ -2684,7 +2691,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2694,12 +2701,12 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C84" s="8"/>
       <c r="D84" s="8"/>
@@ -2708,12 +2715,12 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C85" s="8"/>
       <c r="D85" s="8"/>
@@ -2722,7 +2729,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2736,7 +2743,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2750,12 +2757,12 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B88" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C88" s="8"/>
       <c r="D88" s="8"/>
@@ -2764,7 +2771,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2778,7 +2785,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2790,7 +2797,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2816,9 +2823,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B92" s="9">
         <v>1</v>
@@ -2837,12 +2844,12 @@
         <v>17</v>
       </c>
       <c r="H92" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B93" s="9">
         <v>0.2</v>
@@ -2864,9 +2871,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B94" s="4">
         <v>0.8</v>
@@ -2884,12 +2891,12 @@
         <v>20</v>
       </c>
       <c r="H94" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B95" s="4">
         <v>0.38800000000000001</v>
@@ -2898,7 +2905,7 @@
         <v>18</v>
       </c>
       <c r="D95" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E95" t="s">
         <v>24</v>
@@ -2910,7 +2917,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2920,12 +2927,12 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B97" s="1" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C97" s="8"/>
       <c r="D97" s="8"/>
@@ -2934,12 +2941,12 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B98" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C98" s="8"/>
       <c r="D98" s="8"/>
@@ -2948,7 +2955,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -2962,7 +2969,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2976,12 +2983,12 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B101" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C101" s="8"/>
       <c r="D101" s="8"/>
@@ -2990,7 +2997,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -3004,7 +3011,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3016,7 +3023,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -3042,9 +3049,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B105" s="9">
         <v>1</v>
@@ -3063,12 +3070,12 @@
         <v>17</v>
       </c>
       <c r="H105" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B106" s="9">
         <v>9.6199999999999994E-2</v>
@@ -3087,12 +3094,12 @@
         <v>20</v>
       </c>
       <c r="H106" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B107" s="9">
         <v>1.44E-2</v>
@@ -3111,12 +3118,12 @@
         <v>20</v>
       </c>
       <c r="H107" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B108" s="9">
         <v>0.17899999999999999</v>
@@ -3135,12 +3142,12 @@
         <v>20</v>
       </c>
       <c r="H108" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B109" s="9">
         <v>0.36099999999999999</v>
@@ -3159,12 +3166,12 @@
         <v>20</v>
       </c>
       <c r="H109" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B110" s="9">
         <v>4.5999999999999999E-2</v>
@@ -3183,12 +3190,12 @@
         <v>20</v>
       </c>
       <c r="H110" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B111" s="9">
         <v>0.17</v>
@@ -3207,12 +3214,12 @@
         <v>20</v>
       </c>
       <c r="H111" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B112" s="9">
         <v>0.13300000000000001</v>
@@ -3231,10 +3238,10 @@
         <v>20</v>
       </c>
       <c r="H112" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3244,12 +3251,12 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C114" s="8"/>
       <c r="D114" s="8"/>
@@ -3258,12 +3265,12 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B115" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C115" s="8"/>
       <c r="D115" s="8"/>
@@ -3272,7 +3279,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3286,7 +3293,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3300,12 +3307,12 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B118" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C118" s="8"/>
       <c r="D118" s="8"/>
@@ -3314,7 +3321,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3328,7 +3335,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3340,7 +3347,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3366,9 +3373,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B122" s="9">
         <v>1</v>
@@ -3387,12 +3394,12 @@
         <v>17</v>
       </c>
       <c r="H122" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" t="s">
-        <v>88</v>
       </c>
       <c r="B123" s="9">
         <f>1.5/1000</f>
@@ -3412,12 +3419,12 @@
         <v>20</v>
       </c>
       <c r="H123" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B124" s="9">
         <f>3.5/1000</f>
@@ -3440,9 +3447,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B125" s="13">
         <f>0.13/1000</f>
@@ -3462,12 +3469,12 @@
         <v>20</v>
       </c>
       <c r="H125" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" t="s">
-        <v>92</v>
       </c>
       <c r="B126" s="13">
         <f>0.075/1000</f>
@@ -3487,10 +3494,10 @@
         <v>20</v>
       </c>
       <c r="H126" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -3511,9 +3518,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B128" s="15">
         <f>0.0305/1000</f>
@@ -3532,9 +3539,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B129" s="4">
         <f>-2.45/1000</f>
@@ -3553,10 +3560,10 @@
         <v>20</v>
       </c>
       <c r="H129" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3566,12 +3573,12 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B131" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C131" s="8"/>
       <c r="D131" s="8"/>
@@ -3580,12 +3587,12 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C132" s="8"/>
       <c r="D132" s="8"/>
@@ -3594,7 +3601,7 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
@@ -3608,7 +3615,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3622,12 +3629,12 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C135" s="8"/>
       <c r="D135" s="8"/>
@@ -3636,7 +3643,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3650,7 +3657,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3662,7 +3669,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3688,9 +3695,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B139" s="9">
         <v>1</v>
@@ -3709,12 +3716,12 @@
         <v>17</v>
       </c>
       <c r="H139" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A140" t="s">
-        <v>100</v>
       </c>
       <c r="B140" s="13">
         <v>9.9999999999999995E-7</v>
@@ -3733,7 +3740,7 @@
       </c>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -3754,9 +3761,9 @@
       </c>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B142" s="13">
         <v>3.93E-5</v>
@@ -3775,9 +3782,9 @@
       </c>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B143" s="13">
         <v>2.5799999999999999E-6</v>
@@ -3796,9 +3803,9 @@
       </c>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B144" s="13">
         <v>2.8099999999999999E-7</v>
@@ -3817,9 +3824,9 @@
       </c>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B145" s="13">
         <v>8.8999999999999995E-7</v>
@@ -3838,9 +3845,9 @@
       </c>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B146" s="13">
         <v>8.8999999999999995E-7</v>
@@ -3859,9 +3866,9 @@
       </c>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B147" s="13">
         <v>1.5000000000000001E-12</v>
@@ -3880,9 +3887,9 @@
       </c>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B148" s="13">
         <v>2.4999999999999999E-13</v>
@@ -3901,9 +3908,9 @@
       </c>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B149" s="13">
         <v>9.9999999999999991E-11</v>
@@ -3922,9 +3929,9 @@
       </c>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B150" s="13">
         <v>1.2E-10</v>
@@ -3943,9 +3950,9 @@
       </c>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B151" s="13">
         <v>7.5999999999999999E-13</v>
@@ -3964,9 +3971,9 @@
       </c>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B152" s="13">
         <v>7.5999999999999992E-14</v>
@@ -3985,9 +3992,9 @@
       </c>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B153" s="13">
         <v>5.0999999999999995E-13</v>
@@ -4006,9 +4013,9 @@
       </c>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B154" s="13">
         <v>1.1199999999999999E-11</v>
@@ -4027,9 +4034,9 @@
       </c>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B155" s="13">
         <v>1.5000000000000001E-12</v>
@@ -4048,9 +4055,9 @@
       </c>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B156" s="13">
         <v>5.6000000000000004E-13</v>
@@ -4069,9 +4076,9 @@
       </c>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B157" s="13">
         <v>8.3999999999999995E-13</v>
@@ -4090,9 +4097,9 @@
       </c>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B158" s="13">
         <v>8.3999999999999995E-13</v>
@@ -4111,9 +4118,9 @@
       </c>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B159" s="13">
         <v>8.3999999999999995E-13</v>
@@ -4132,7 +4139,7 @@
       </c>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4142,12 +4149,12 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B161" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C161" s="8"/>
       <c r="D161" s="8"/>
@@ -4157,12 +4164,12 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B162" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C162" s="8"/>
       <c r="D162" s="8"/>
@@ -4172,7 +4179,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
@@ -4187,7 +4194,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4202,12 +4209,12 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B165" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C165" s="8"/>
       <c r="D165" s="8"/>
@@ -4217,7 +4224,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4232,7 +4239,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4245,7 +4252,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4272,7 +4279,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4295,9 +4302,9 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A170" s="8" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B170" s="13">
         <v>1.4039999999999999E-5</v>
@@ -4307,10 +4314,10 @@
       </c>
       <c r="D170" s="8"/>
       <c r="E170" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="F170" s="8" t="s">
         <v>125</v>
-      </c>
-      <c r="F170" s="8" t="s">
-        <v>126</v>
       </c>
       <c r="G170" s="8" t="s">
         <v>31</v>
@@ -4319,9 +4326,9 @@
       <c r="I170" s="8"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A171" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B171" s="9">
         <v>1.155E-2</v>
@@ -4334,7 +4341,7 @@
         <v>9</v>
       </c>
       <c r="F171" s="8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G171" s="8" t="s">
         <v>31</v>
@@ -4343,9 +4350,9 @@
       <c r="I171" s="8"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A172" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B172" s="13">
         <v>8.5109999999999986E-6</v>
@@ -4355,10 +4362,10 @@
       </c>
       <c r="D172" s="8"/>
       <c r="E172" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F172" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G172" s="8" t="s">
         <v>31</v>
@@ -4367,9 +4374,9 @@
       <c r="I172" s="8"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A173" s="8" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B173" s="13">
         <v>8.5109999999999986E-6</v>
@@ -4379,10 +4386,10 @@
       </c>
       <c r="D173" s="8"/>
       <c r="E173" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F173" s="8" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G173" s="8" t="s">
         <v>31</v>
@@ -4391,9 +4398,9 @@
       <c r="I173" s="8"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A174" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B174" s="9">
         <v>1</v>
@@ -4412,14 +4419,14 @@
         <v>17</v>
       </c>
       <c r="H174" s="8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I174" s="8"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A175" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B175" s="13">
         <v>9.8720000000000014E-6</v>
@@ -4438,14 +4445,14 @@
         <v>20</v>
       </c>
       <c r="H175" s="8" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="I175" s="8"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A176" s="8" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B176" s="13">
         <v>4.7780000000000002E-8</v>
@@ -4464,14 +4471,14 @@
         <v>20</v>
       </c>
       <c r="H176" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I176" s="8"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A177" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B177" s="13">
         <v>1.9410000000000001E-6</v>
@@ -4490,14 +4497,14 @@
         <v>20</v>
       </c>
       <c r="H177" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="I177" s="8"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A178" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B178" s="9">
         <v>1.409E-2</v>
@@ -4516,14 +4523,14 @@
         <v>20</v>
       </c>
       <c r="H178" s="8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="I178" s="8"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A179" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B179" s="13">
         <v>1.021E-3</v>
@@ -4542,14 +4549,14 @@
         <v>20</v>
       </c>
       <c r="H179" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="I179" s="8"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A180" s="8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B180" s="13">
         <v>1.3140000000000001E-3</v>
@@ -4561,21 +4568,21 @@
         <v>19</v>
       </c>
       <c r="E180" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F180" s="8"/>
       <c r="G180" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H180" s="8" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="I180" s="8"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A181" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B181" s="13">
         <v>8.2189999999999997E-8</v>
@@ -4587,21 +4594,21 @@
         <v>4</v>
       </c>
       <c r="E181" s="8" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="F181" s="8"/>
       <c r="G181" s="8" t="s">
         <v>20</v>
       </c>
       <c r="H181" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="I181" s="8"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A182" s="8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B182" s="13">
         <v>1.9740000000000001E-5</v>
@@ -4620,14 +4627,14 @@
         <v>20</v>
       </c>
       <c r="H182" s="8" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I182" s="8"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A183" s="8" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B183" s="13">
         <v>1.021E-3</v>
@@ -4646,14 +4653,14 @@
         <v>20</v>
       </c>
       <c r="H183" s="8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I183" s="8"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A184" s="8" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B184" s="13">
         <v>1.7350000000000002E-5</v>
@@ -4672,14 +4679,14 @@
         <v>20</v>
       </c>
       <c r="H184" s="8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="I184" s="8"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A185" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B185" s="13">
         <v>3.6990000000000003E-5</v>
@@ -4698,14 +4705,14 @@
         <v>20</v>
       </c>
       <c r="H185" s="8" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I185" s="8"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A186" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B186" s="9">
         <v>-4.731E-3</v>
@@ -4724,12 +4731,12 @@
         <v>20</v>
       </c>
       <c r="H186" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I186" s="8"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4740,12 +4747,12 @@
       <c r="H187" s="2"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C188" s="8"/>
       <c r="D188" s="8"/>
@@ -4755,12 +4762,12 @@
       <c r="H188" s="8"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B189" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C189" s="8"/>
       <c r="D189" s="8"/>
@@ -4770,7 +4777,7 @@
       <c r="H189" s="8"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
@@ -4784,7 +4791,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4798,12 +4805,12 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B192" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C192" s="8"/>
       <c r="D192" s="8"/>
@@ -4812,7 +4819,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4826,7 +4833,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4838,7 +4845,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4864,9 +4871,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B196" s="9">
         <v>1</v>
@@ -4885,12 +4892,12 @@
         <v>17</v>
       </c>
       <c r="H196" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A197" s="8" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" s="8" t="s">
-        <v>122</v>
       </c>
       <c r="B197" s="9">
         <v>1</v>
@@ -4909,12 +4916,12 @@
         <v>20</v>
       </c>
       <c r="H197" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B198" s="4">
         <f>13.1/1000</f>
@@ -4924,7 +4931,7 @@
         <v>18</v>
       </c>
       <c r="D198" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E198" t="s">
         <v>24</v>
@@ -4936,7 +4943,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
         <v>29</v>
       </c>
@@ -4959,7 +4966,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4969,12 +4976,12 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B201" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C201" s="8"/>
       <c r="D201" s="8"/>
@@ -4983,12 +4990,12 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B202" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C202" s="8"/>
       <c r="D202" s="8"/>
@@ -4997,7 +5004,7 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
@@ -5011,7 +5018,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -5025,12 +5032,12 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B205" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C205" s="8"/>
       <c r="D205" s="8"/>
@@ -5039,7 +5046,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -5053,7 +5060,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -5065,7 +5072,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5091,9 +5098,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B209" s="9">
         <v>1</v>
@@ -5112,12 +5119,12 @@
         <v>17</v>
       </c>
       <c r="H209" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B210" s="9">
         <v>1</v>
@@ -5136,12 +5143,12 @@
         <v>20</v>
       </c>
       <c r="H210" s="8" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B211" s="4">
         <f>3.99/1000</f>
@@ -5151,7 +5158,7 @@
         <v>18</v>
       </c>
       <c r="D211" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E211" t="s">
         <v>24</v>
@@ -5163,7 +5170,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -5186,7 +5193,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5196,12 +5203,12 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B214" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C214" s="8"/>
       <c r="D214" s="8"/>
@@ -5210,12 +5217,12 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B215" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C215" s="8"/>
       <c r="D215" s="8"/>
@@ -5224,7 +5231,7 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
@@ -5238,7 +5245,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5252,12 +5259,12 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B218" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C218" s="8"/>
       <c r="D218" s="8"/>
@@ -5266,7 +5273,7 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
@@ -5280,7 +5287,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5292,7 +5299,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5318,9 +5325,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B222" s="9">
         <v>1</v>
@@ -5339,12 +5346,12 @@
         <v>17</v>
       </c>
       <c r="H222" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B223" s="9">
         <v>6.7299999999999999E-2</v>
@@ -5363,12 +5370,12 @@
         <v>20</v>
       </c>
       <c r="H223" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B224" s="9">
         <v>6.7299999999999999E-2</v>
@@ -5387,12 +5394,12 @@
         <v>20</v>
       </c>
       <c r="H224" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="8" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B225" s="9">
         <v>1.27</v>
@@ -5411,12 +5418,12 @@
         <v>20</v>
       </c>
       <c r="H225" s="8" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B226" s="9">
         <v>1.0500000000000001E-2</v>
@@ -5435,10 +5442,10 @@
         <v>20</v>
       </c>
       <c r="H226" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -5460,7 +5467,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5470,12 +5477,12 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B229" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C229" s="8"/>
       <c r="D229" s="8"/>
@@ -5484,12 +5491,12 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B230" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C230" s="8"/>
       <c r="D230" s="8"/>
@@ -5498,7 +5505,7 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
@@ -5512,7 +5519,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5526,12 +5533,12 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B233" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C233" s="8"/>
       <c r="D233" s="8"/>
@@ -5540,7 +5547,7 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
@@ -5554,7 +5561,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5566,7 +5573,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5592,9 +5599,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="8" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B237" s="9">
         <v>1</v>
@@ -5613,12 +5620,12 @@
         <v>17</v>
       </c>
       <c r="H237" s="8" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B238" s="9">
         <v>0.35699999999999998</v>
@@ -5637,12 +5644,12 @@
         <v>20</v>
       </c>
       <c r="H238" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="8" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B239" s="9">
         <v>0.35699999999999998</v>
@@ -5661,12 +5668,12 @@
         <v>20</v>
       </c>
       <c r="H239" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B240" s="4">
         <v>1.06</v>
@@ -5675,7 +5682,7 @@
         <v>18</v>
       </c>
       <c r="D240" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E240" t="s">
         <v>24</v>
@@ -5687,9 +5694,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B241" s="9">
         <v>1.46</v>
@@ -5708,10 +5715,10 @@
         <v>20</v>
       </c>
       <c r="H241" s="8" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>29</v>
       </c>
@@ -5733,7 +5740,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5743,7 +5750,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5757,12 +5764,12 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B245" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C245" s="8"/>
       <c r="D245" s="8"/>
@@ -5771,7 +5778,7 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
@@ -5785,7 +5792,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5799,7 +5806,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5813,7 +5820,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5827,7 +5834,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5839,7 +5846,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5865,7 +5872,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5889,9 +5896,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B253" s="6">
         <v>4.4321789115451698E-10</v>
@@ -5910,10 +5917,10 @@
         <v>20</v>
       </c>
       <c r="H253" s="7" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5935,7 +5942,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5958,7 +5965,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5968,12 +5975,12 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B257" s="19" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C257" s="20"/>
       <c r="D257" s="5"/>
@@ -5982,12 +5989,12 @@
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B258" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C258" s="20"/>
       <c r="D258" s="5"/>
@@ -5996,7 +6003,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
@@ -6010,12 +6017,12 @@
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B260" s="17" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C260" s="20"/>
       <c r="D260" s="5"/>
@@ -6024,7 +6031,7 @@
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
@@ -6038,7 +6045,7 @@
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
@@ -6052,9 +6059,9 @@
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B263" s="5"/>
       <c r="C263" s="20"/>
@@ -6064,7 +6071,7 @@
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
@@ -6076,7 +6083,7 @@
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
@@ -6102,9 +6109,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B266" s="22">
         <v>1</v>
@@ -6123,12 +6130,12 @@
         <v>17</v>
       </c>
       <c r="H266" s="17" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B267" s="23">
         <v>2.8998115122517001E-2</v>
@@ -6150,9 +6157,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="17" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B268" s="6">
         <v>1.1684210526315801E-3</v>
@@ -6160,8 +6167,8 @@
       <c r="C268" t="s">
         <v>18</v>
       </c>
-      <c r="D268" s="17" t="s">
-        <v>44</v>
+      <c r="D268" t="s">
+        <v>4</v>
       </c>
       <c r="E268" s="17" t="s">
         <v>24</v>
@@ -6171,12 +6178,12 @@
         <v>20</v>
       </c>
       <c r="H268" s="18" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A269" s="17" t="s">
         <v>203</v>
-      </c>
-    </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A269" s="17" t="s">
-        <v>204</v>
       </c>
       <c r="B269" s="6">
         <v>2.9473684210526402E-9</v>
@@ -6195,12 +6202,12 @@
         <v>20</v>
       </c>
       <c r="H269" s="18" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A270" s="17" t="s">
         <v>205</v>
-      </c>
-    </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A270" s="17" t="s">
-        <v>206</v>
       </c>
       <c r="B270" s="24">
         <v>5.3052631578947428E-2</v>
@@ -6219,10 +6226,10 @@
         <v>20</v>
       </c>
       <c r="H270" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -6237,15 +6244,15 @@
         <v>9</v>
       </c>
       <c r="F271" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G271" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B272" s="15">
         <v>2.2105263157894801E-6</v>
@@ -6258,15 +6265,15 @@
         <v>9</v>
       </c>
       <c r="F272" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G272" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B273" s="15">
         <v>2.10526315789474E-6</v>
@@ -6279,15 +6286,15 @@
         <v>9</v>
       </c>
       <c r="F273" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G273" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A274" s="18" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B274" s="15">
         <v>1.05263157894737E-7</v>
@@ -6300,13 +6307,13 @@
         <v>9</v>
       </c>
       <c r="F274" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G274" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>37</v>
       </c>
@@ -6321,15 +6328,15 @@
         <v>9</v>
       </c>
       <c r="F275" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G275" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A276" s="18" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B276" s="15">
         <v>5.7894736842105305E-7</v>
@@ -6342,15 +6349,15 @@
         <v>9</v>
       </c>
       <c r="F276" s="25" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G276" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A277" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B277" s="15">
         <v>2.1052631578947401E-7</v>
@@ -6363,15 +6370,15 @@
         <v>9</v>
       </c>
       <c r="F277" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G277" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A278" s="18" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B278" s="15">
         <v>1.05263157894737E-9</v>
@@ -6384,15 +6391,15 @@
         <v>9</v>
       </c>
       <c r="F278" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G278" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A279" s="18" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B279" s="15">
         <v>1.5789473684210501E-7</v>
@@ -6405,15 +6412,15 @@
         <v>9</v>
       </c>
       <c r="F279" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G279" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A280" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B280" s="15">
         <v>4.2105263157894802E-7</v>
@@ -6426,15 +6433,15 @@
         <v>9</v>
       </c>
       <c r="F280" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G280" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A281" s="18" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B281" s="15">
         <v>1.0526315789473699E-11</v>
@@ -6447,15 +6454,15 @@
         <v>9</v>
       </c>
       <c r="F281" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G281" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A282" s="18" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B282" s="15">
         <v>7.3684210526315899E-7</v>
@@ -6468,15 +6475,15 @@
         <v>9</v>
       </c>
       <c r="F282" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G282" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A283" s="18" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B283" s="6">
         <v>0</v>
@@ -6488,15 +6495,15 @@
         <v>9</v>
       </c>
       <c r="F283" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G283" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A284" s="18" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B284" s="15">
         <v>1.05263157894737E-7</v>
@@ -6508,15 +6515,15 @@
         <v>9</v>
       </c>
       <c r="F284" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G284" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A285" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B285" s="15">
         <v>3.1578947368421103E-11</v>
@@ -6528,15 +6535,15 @@
         <v>9</v>
       </c>
       <c r="F285" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G285" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A286" s="18" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B286" s="15">
         <v>1.0526315789473701E-8</v>
@@ -6548,15 +6555,15 @@
         <v>9</v>
       </c>
       <c r="F286" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G286" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A287" s="18" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B287" s="15">
         <v>1.2631578947368401E-6</v>
@@ -6568,15 +6575,15 @@
         <v>9</v>
       </c>
       <c r="F287" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G287" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A288" s="18" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B288" s="15">
         <v>2.1052631578947401E-7</v>
@@ -6588,15 +6595,15 @@
         <v>9</v>
       </c>
       <c r="F288" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G288" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="18" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B289" s="15">
         <v>2.1052631578947401E-8</v>
@@ -6608,15 +6615,15 @@
         <v>9</v>
       </c>
       <c r="F289" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G289" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="18" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B290" s="15">
         <v>2.1052631578947401E-7</v>
@@ -6628,13 +6635,13 @@
         <v>9</v>
       </c>
       <c r="F290" s="17" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G290" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="3"/>
@@ -6644,12 +6651,12 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="19" t="s">
         <v>0</v>
       </c>
       <c r="B292" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C292" s="20"/>
       <c r="D292" s="5"/>
@@ -6658,12 +6665,12 @@
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="19" t="s">
         <v>2</v>
       </c>
       <c r="B293" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C293" s="20"/>
       <c r="D293" s="5"/>
@@ -6672,7 +6679,7 @@
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="19" t="s">
         <v>3</v>
       </c>
@@ -6686,12 +6693,12 @@
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B295" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C295" s="20"/>
       <c r="D295" s="5"/>
@@ -6700,7 +6707,7 @@
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="19" t="s">
         <v>5</v>
       </c>
@@ -6714,7 +6721,7 @@
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="19" t="s">
         <v>8</v>
       </c>
@@ -6728,7 +6735,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="19" t="s">
         <v>10</v>
       </c>
@@ -6740,7 +6747,7 @@
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="5" t="s">
         <v>11</v>
       </c>
@@ -6766,9 +6773,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="17" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B300" s="22">
         <v>1</v>
@@ -6787,12 +6794,12 @@
         <v>17</v>
       </c>
       <c r="H300" s="17" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B301" s="22">
         <v>0.38400000000000001</v>
@@ -6801,7 +6808,7 @@
         <v>18</v>
       </c>
       <c r="D301" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E301" t="s">
         <v>24</v>
@@ -6814,9 +6821,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B302" s="15">
         <v>8.2699999999999996E-11</v>
@@ -6834,12 +6841,12 @@
         <v>20</v>
       </c>
       <c r="H302" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A303" t="s">
         <v>226</v>
-      </c>
-    </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A303" t="s">
-        <v>227</v>
       </c>
       <c r="B303" s="15">
         <v>7.4400000000000002E-10</v>
@@ -6857,12 +6864,12 @@
         <v>20</v>
       </c>
       <c r="H303" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A304" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A304" t="s">
-        <v>229</v>
       </c>
       <c r="B304" s="15">
         <v>8.2600000000000002E-5</v>
@@ -6880,12 +6887,12 @@
         <v>20</v>
       </c>
       <c r="H304" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305" t="s">
         <v>230</v>
-      </c>
-    </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A305" t="s">
-        <v>231</v>
       </c>
       <c r="B305" s="15">
         <v>3.3099999999999999E-10</v>
@@ -6903,12 +6910,12 @@
         <v>20</v>
       </c>
       <c r="H305" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A306" t="s">
-        <v>233</v>
       </c>
       <c r="B306" s="15">
         <v>5.1400000000000003E-12</v>
@@ -6926,12 +6933,12 @@
         <v>20</v>
       </c>
       <c r="H306" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B307" s="15">
         <v>2.8400000000000002E-4</v>
@@ -6949,12 +6956,12 @@
         <v>20</v>
       </c>
       <c r="H307" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B308" s="15">
         <v>5.7899999999999997E-10</v>
@@ -6972,12 +6979,12 @@
         <v>20</v>
       </c>
       <c r="H308" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B309" s="15">
         <v>3.0400000000000002E-4</v>
@@ -6995,12 +7002,12 @@
         <v>20</v>
       </c>
       <c r="H309" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B310" s="15">
         <v>-2.2699999999999999E-4</v>
@@ -7009,7 +7016,7 @@
         <v>18</v>
       </c>
       <c r="D310" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E310" t="s">
         <v>9</v>
@@ -7018,7 +7025,7 @@
         <v>20</v>
       </c>
       <c r="H310" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>
@@ -7030,17 +7037,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7054,12 +7061,12 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -7068,7 +7075,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -7082,7 +7089,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -7096,7 +7103,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -7110,7 +7117,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -7124,7 +7131,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -7136,7 +7143,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -7162,7 +7169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -7186,9 +7193,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="9">
         <v>0.62178</v>
@@ -7210,9 +7217,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B11" s="9">
         <v>13.952</v>
@@ -7231,12 +7238,12 @@
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="4">
         <v>4.9231999999999998E-2</v>
@@ -7245,7 +7252,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
@@ -7257,9 +7264,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B13" s="13">
         <v>3.4820000000000001E-4</v>
@@ -7281,9 +7288,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B14" s="4">
         <v>0.71728999999999998</v>
@@ -7304,9 +7311,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B15" s="15">
         <v>2.9845513851461699E-5</v>
@@ -7325,10 +7332,10 @@
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -7351,9 +7358,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B17" s="13">
         <v>-1.9897009234307801E-4</v>
@@ -7371,10 +7378,10 @@
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7388,13 +7395,13 @@
         <v>9</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G18" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7408,13 +7415,13 @@
         <v>21</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -7428,14 +7435,14 @@
         <v>9</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7449,14 +7456,14 @@
         <v>9</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G21" t="s">
         <v>31</v>
       </c>
       <c r="H21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7470,13 +7477,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G22" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7496,7 +7503,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -7506,12 +7513,12 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -7520,12 +7527,12 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -7534,7 +7541,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -7548,7 +7555,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
@@ -7562,7 +7569,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
@@ -7576,7 +7583,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -7590,7 +7597,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -7602,7 +7609,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
@@ -7628,9 +7635,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B33" s="9">
         <v>1</v>
@@ -7652,9 +7659,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B34" s="9">
         <v>0.62178</v>
@@ -7676,9 +7683,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="9">
         <v>13.952</v>
@@ -7697,12 +7704,12 @@
         <v>20</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B36" s="4">
         <v>4.9231999999999998E-2</v>
@@ -7711,7 +7718,7 @@
         <v>18</v>
       </c>
       <c r="D36" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E36" t="s">
         <v>24</v>
@@ -7723,9 +7730,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B37" s="13">
         <v>3.4820000000000001E-4</v>
@@ -7747,9 +7754,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B38" s="4">
         <v>0.71728999999999998</v>
@@ -7770,9 +7777,9 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B39" s="15">
         <v>2.9845513851461699E-5</v>
@@ -7791,10 +7798,10 @@
         <v>20</v>
       </c>
       <c r="H39" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -7817,9 +7824,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="14" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B41" s="13">
         <v>-1.9897009234307801E-4</v>
@@ -7837,10 +7844,10 @@
         <v>20</v>
       </c>
       <c r="H41" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -7854,13 +7861,13 @@
         <v>9</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G42" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -7874,13 +7881,13 @@
         <v>21</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G43" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -7894,14 +7901,14 @@
         <v>9</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G44" t="s">
         <v>31</v>
       </c>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -7915,14 +7922,14 @@
         <v>9</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G45" t="s">
         <v>31</v>
       </c>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -7936,13 +7943,13 @@
         <v>21</v>
       </c>
       <c r="F46" s="17" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G46" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -7962,7 +7969,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
@@ -7972,12 +7979,12 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C49" s="8"/>
       <c r="D49" s="8"/>
@@ -7986,12 +7993,12 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C50" s="8"/>
       <c r="D50" s="8"/>
@@ -8000,7 +8007,7 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="8" t="s">
         <v>3</v>
       </c>
@@ -8014,7 +8021,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="8" t="s">
         <v>5</v>
       </c>
@@ -8028,7 +8035,7 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="8" t="s">
         <v>6</v>
       </c>
@@ -8042,7 +8049,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="8" t="s">
         <v>8</v>
       </c>
@@ -8056,7 +8063,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
@@ -8068,7 +8075,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="8" t="s">
         <v>11</v>
       </c>
@@ -8094,9 +8101,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B57" s="9">
         <v>1</v>
@@ -8118,7 +8125,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="8" t="s">
         <v>40</v>
       </c>
@@ -8142,9 +8149,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B59" s="13">
         <v>5.5099999999999998E-5</v>
@@ -8163,10 +8170,10 @@
         <v>20</v>
       </c>
       <c r="H59" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -8190,7 +8197,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -8210,9 +8217,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B62" s="4">
         <v>0.55600000000000005</v>
@@ -8221,7 +8228,7 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E62" t="s">
         <v>24</v>
@@ -8233,7 +8240,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -8253,7 +8260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>35</v>
       </c>
@@ -8273,7 +8280,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -8293,7 +8300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -8314,7 +8321,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -8335,9 +8342,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B68" s="15">
         <v>-5.5099999999999998E-5</v>
@@ -8355,44 +8362,43 @@
         <v>20</v>
       </c>
       <c r="H68" s="8" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="28"/>
+        <v>154</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B69" s="15"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B74" s="15"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="8"/>
       <c r="B80" s="13"/>
       <c r="C80" s="8"/>
@@ -8410,22 +8416,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="86.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -8434,12 +8440,12 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C2" s="8"/>
       <c r="D2" s="8"/>
@@ -8448,7 +8454,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8462,7 +8468,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8476,12 +8482,12 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -8490,7 +8496,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8504,7 +8510,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8516,7 +8522,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8542,9 +8548,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B9" s="9">
         <v>1</v>
@@ -8563,12 +8569,12 @@
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B10" s="9">
         <v>0.65178999999999998</v>
@@ -8590,9 +8596,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B11" s="9">
         <v>6.93</v>
@@ -8611,12 +8617,12 @@
         <v>20</v>
       </c>
       <c r="H11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B12" s="4">
         <v>7.3999999999999996E-2</v>
@@ -8625,7 +8631,7 @@
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E12" t="s">
         <v>24</v>
@@ -8637,9 +8643,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B13" s="13">
         <v>3.0000000000000001E-5</v>
@@ -8658,12 +8664,12 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>178</v>
       </c>
       <c r="B14" s="13">
         <v>1.0000000000000001E-5</v>
@@ -8682,12 +8688,12 @@
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B15" s="13">
         <v>9.0000000000000006E-5</v>
@@ -8706,12 +8712,12 @@
         <v>20</v>
       </c>
       <c r="H15" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B16" s="13">
         <v>2.0000000000000002E-5</v>
@@ -8733,9 +8739,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B17" s="4">
         <f>0.2+0.00071996+0.64928</f>
@@ -8754,12 +8760,12 @@
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B18" s="13">
         <f>0.00020525+0.000034749</f>
@@ -8779,12 +8785,12 @@
         <v>20</v>
       </c>
       <c r="H18" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B19" s="13">
         <v>3.7199999999999998E-11</v>
@@ -8802,12 +8808,12 @@
         <v>20</v>
       </c>
       <c r="H19" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B20" s="13">
         <v>9.7999999999999997E-4</v>
@@ -8819,13 +8825,13 @@
         <v>9</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G20" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8845,9 +8851,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B22" s="13">
         <v>1.9999999999999999E-6</v>
@@ -8865,7 +8871,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -8879,13 +8885,13 @@
         <v>9</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G23" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -8905,9 +8911,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B25" s="13">
         <v>1.8000000000000001E-4</v>
@@ -8925,9 +8931,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B26" s="15">
         <v>3.0000000000000001E-5</v>
@@ -8945,9 +8951,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B27" s="15">
         <v>2.4000000000000001E-4</v>
@@ -8965,9 +8971,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B28" s="15">
         <v>9.9999999999999995E-7</v>
@@ -8985,9 +8991,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B29" s="15">
         <v>5.2999999999999998E-4</v>
@@ -8999,13 +9005,13 @@
         <v>9</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G29" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -9025,9 +9031,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B31" s="15">
         <v>2.0000000000000002E-5</v>
@@ -9045,9 +9051,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B32" s="15">
         <v>2.4000000000000001E-4</v>
@@ -9065,9 +9071,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B33" s="15">
         <v>1.38E-5</v>
@@ -9079,15 +9085,15 @@
         <v>9</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G33" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B34" s="15">
         <v>1E-4</v>
@@ -9105,9 +9111,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B35" s="15">
         <v>1.0000000000000001E-5</v>
@@ -9125,9 +9131,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B36" s="15">
         <v>4.8999999999999998E-4</v>
@@ -9146,9 +9152,9 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B37" s="13">
         <v>1.0000000000000001E-5</v>
@@ -9168,7 +9174,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9178,12 +9184,12 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C39" s="8"/>
       <c r="D39" s="8"/>
@@ -9192,12 +9198,12 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C40" s="8"/>
       <c r="D40" s="8"/>
@@ -9206,7 +9212,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9220,7 +9226,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9234,12 +9240,12 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
       <c r="B43" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8"/>
@@ -9248,7 +9254,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9262,7 +9268,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9274,7 +9280,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9300,9 +9306,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B47" s="9">
         <v>1</v>
@@ -9321,12 +9327,12 @@
         <v>17</v>
       </c>
       <c r="H47" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B48" s="9">
         <v>0.65178999999999998</v>
@@ -9348,9 +9354,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="17" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B49" s="22">
         <v>6.93</v>
@@ -9369,12 +9375,12 @@
         <v>20</v>
       </c>
       <c r="H49" s="17" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B50" s="4">
         <v>7.3999999999999996E-2</v>
@@ -9383,7 +9389,7 @@
         <v>18</v>
       </c>
       <c r="D50" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E50" t="s">
         <v>24</v>
@@ -9395,9 +9401,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B51" s="13">
         <v>3.0000000000000001E-5</v>
@@ -9416,12 +9422,12 @@
         <v>20</v>
       </c>
       <c r="H51" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>178</v>
       </c>
       <c r="B52" s="13">
         <v>1.0000000000000001E-5</v>
@@ -9440,12 +9446,12 @@
         <v>20</v>
       </c>
       <c r="H52" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B53" s="13">
         <v>9.0000000000000006E-5</v>
@@ -9464,12 +9470,12 @@
         <v>20</v>
       </c>
       <c r="H53" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B54" s="13">
         <v>2.0000000000000002E-5</v>
@@ -9491,9 +9497,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B55" s="4">
         <f>0.2+0.00071996+0.64928</f>
@@ -9512,12 +9518,12 @@
         <v>20</v>
       </c>
       <c r="H55" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B56" s="13">
         <f>0.00020525+0.000034749</f>
@@ -9537,12 +9543,12 @@
         <v>20</v>
       </c>
       <c r="H56" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B57" s="13">
         <v>3.7199999999999998E-11</v>
@@ -9560,12 +9566,12 @@
         <v>20</v>
       </c>
       <c r="H57" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B58" s="13">
         <v>9.7999999999999997E-4</v>
@@ -9577,13 +9583,13 @@
         <v>9</v>
       </c>
       <c r="F58" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G58" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9603,9 +9609,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B60" s="13">
         <v>1.9999999999999999E-6</v>
@@ -9623,7 +9629,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9637,13 +9643,13 @@
         <v>9</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G61" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9663,9 +9669,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B63" s="13">
         <v>1.8000000000000001E-4</v>
@@ -9683,9 +9689,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B64" s="15">
         <v>3.0000000000000001E-5</v>
@@ -9703,9 +9709,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B65" s="15">
         <v>2.4000000000000001E-4</v>
@@ -9723,9 +9729,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B66" s="15">
         <v>9.9999999999999995E-7</v>
@@ -9743,9 +9749,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B67" s="15">
         <v>5.2999999999999998E-4</v>
@@ -9757,13 +9763,13 @@
         <v>9</v>
       </c>
       <c r="F67" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G67" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -9783,9 +9789,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B69" s="15">
         <v>2.0000000000000002E-5</v>
@@ -9803,9 +9809,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B70" s="15">
         <v>2.4000000000000001E-4</v>
@@ -9823,9 +9829,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B71" s="15">
         <v>1.38E-5</v>
@@ -9837,15 +9843,15 @@
         <v>9</v>
       </c>
       <c r="F71" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="G71" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B72" s="15">
         <v>1E-4</v>
@@ -9863,9 +9869,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B73" s="15">
         <v>1.0000000000000001E-5</v>
@@ -9883,9 +9889,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B74" s="15">
         <v>4.8999999999999998E-4</v>
@@ -9904,9 +9910,9 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B75" s="13">
         <v>1.0000000000000001E-5</v>
@@ -9935,34 +9941,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9970,7 +9976,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -9978,15 +9984,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -9994,12 +10000,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10025,9 +10031,9 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B9" s="4">
         <v>1</v>
@@ -10045,12 +10051,12 @@
         <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B10" s="4">
         <v>2.5190000000000001</v>
@@ -10068,12 +10074,12 @@
         <v>20</v>
       </c>
       <c r="H10" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="4">
         <v>0.14300000000000002</v>
@@ -10082,7 +10088,7 @@
         <v>18</v>
       </c>
       <c r="D11" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="E11" t="s">
         <v>24</v>
@@ -10095,7 +10101,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10117,9 +10123,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B13" s="4">
         <v>2.2000000000000002E-2</v>
@@ -10137,12 +10143,12 @@
         <v>20</v>
       </c>
       <c r="H13" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B14" s="15">
         <v>2.0789999999999999E-5</v>
@@ -10160,10 +10166,10 @@
         <v>20</v>
       </c>
       <c r="H14" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10183,7 +10189,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -10203,9 +10209,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B17" s="4">
         <v>-1.474E-3</v>
@@ -10223,12 +10229,12 @@
         <v>20</v>
       </c>
       <c r="H17" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" s="15">
         <v>2.0789999999999999E-5</v>

--- a/Raw data/lci-Abhi image SSP2-Base 2020 latest without electricity.xlsx
+++ b/Raw data/lci-Abhi image SSP2-Base 2020 latest without electricity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11116"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20404"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abhinabera/Desktop/Prospective-LCA/Raw data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anabera\Desktop\Ongoing projects\Prospective LCA\Raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A15AC727-938F-BE46-9E40-CB4D8E2191C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2568898-DD79-4343-A65B-EAD8C7AF4B8E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" activeTab="1" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
+    <workbookView xWindow="0" yWindow="495" windowWidth="28800" windowHeight="17505" xr2:uid="{79F87D26-5407-4579-9D8D-FA563FE5FD90}"/>
   </bookViews>
   <sheets>
     <sheet name="Utilities" sheetId="6" r:id="rId1"/>
@@ -22,17 +22,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -1239,19 +1228,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55E8D1F9-2651-4D58-AB8D-D63402B2F76A}">
   <dimension ref="A1:K310"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="70.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.6640625" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="70.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>44</v>
       </c>
@@ -1265,7 +1254,7 @@
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="3"/>
@@ -1275,7 +1264,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1289,7 +1278,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>2</v>
       </c>
@@ -1303,7 +1292,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>3</v>
       </c>
@@ -1317,7 +1306,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>5</v>
       </c>
@@ -1331,7 +1320,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
@@ -1345,7 +1334,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>8</v>
       </c>
@@ -1359,7 +1348,7 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -1371,7 +1360,7 @@
       <c r="G9" s="8"/>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>11</v>
       </c>
@@ -1397,7 +1386,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>50</v>
       </c>
@@ -1421,7 +1410,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -1445,7 +1434,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>54</v>
       </c>
@@ -1468,7 +1457,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -1478,7 +1467,7 @@
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>0</v>
       </c>
@@ -1492,7 +1481,7 @@
       <c r="G15" s="8"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>2</v>
       </c>
@@ -1506,7 +1495,7 @@
       <c r="G16" s="8"/>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>3</v>
       </c>
@@ -1520,7 +1509,7 @@
       <c r="G17" s="8"/>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>5</v>
       </c>
@@ -1534,7 +1523,7 @@
       <c r="G18" s="8"/>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>6</v>
       </c>
@@ -1548,7 +1537,7 @@
       <c r="G19" s="8"/>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>8</v>
       </c>
@@ -1562,7 +1551,7 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>10</v>
       </c>
@@ -1574,7 +1563,7 @@
       <c r="G21" s="8"/>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>11</v>
       </c>
@@ -1600,7 +1589,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1624,7 +1613,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>57</v>
       </c>
@@ -1648,7 +1637,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>59</v>
       </c>
@@ -1671,7 +1660,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>61</v>
       </c>
@@ -1694,7 +1683,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>54</v>
       </c>
@@ -1717,7 +1706,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="3"/>
@@ -1727,7 +1716,7 @@
       <c r="G28" s="2"/>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>0</v>
       </c>
@@ -1741,7 +1730,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>2</v>
       </c>
@@ -1755,7 +1744,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
         <v>3</v>
       </c>
@@ -1769,7 +1758,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>5</v>
       </c>
@@ -1783,7 +1772,7 @@
       <c r="G32" s="8"/>
       <c r="H32" s="8"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
         <v>6</v>
       </c>
@@ -1797,7 +1786,7 @@
       <c r="G33" s="8"/>
       <c r="H33" s="8"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
         <v>8</v>
       </c>
@@ -1811,7 +1800,7 @@
       <c r="G34" s="8"/>
       <c r="H34" s="8"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>10</v>
       </c>
@@ -1823,7 +1812,7 @@
       <c r="G35" s="8"/>
       <c r="H35" s="8"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>11</v>
       </c>
@@ -1849,7 +1838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>62</v>
       </c>
@@ -1873,7 +1862,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>64</v>
       </c>
@@ -1897,7 +1886,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>66</v>
       </c>
@@ -1920,7 +1909,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>68</v>
       </c>
@@ -1943,7 +1932,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>54</v>
       </c>
@@ -1966,7 +1955,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="3"/>
@@ -1976,7 +1965,7 @@
       <c r="G42" s="2"/>
       <c r="H42" s="2"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>0</v>
       </c>
@@ -1990,7 +1979,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>2</v>
       </c>
@@ -2004,7 +1993,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>3</v>
       </c>
@@ -2018,7 +2007,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>5</v>
       </c>
@@ -2032,7 +2021,7 @@
       <c r="G46" s="8"/>
       <c r="H46" s="8"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>6</v>
       </c>
@@ -2046,7 +2035,7 @@
       <c r="G47" s="8"/>
       <c r="H47" s="8"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
         <v>8</v>
       </c>
@@ -2060,7 +2049,7 @@
       <c r="G48" s="8"/>
       <c r="H48" s="8"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>10</v>
       </c>
@@ -2072,7 +2061,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>11</v>
       </c>
@@ -2098,7 +2087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>70</v>
       </c>
@@ -2122,7 +2111,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>52</v>
       </c>
@@ -2146,7 +2135,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -2169,7 +2158,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -2192,7 +2181,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>54</v>
       </c>
@@ -2215,7 +2204,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
       <c r="C56" s="3"/>
@@ -2225,7 +2214,7 @@
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>0</v>
       </c>
@@ -2239,7 +2228,7 @@
       <c r="G57" s="8"/>
       <c r="H57" s="8"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>2</v>
       </c>
@@ -2253,7 +2242,7 @@
       <c r="G58" s="8"/>
       <c r="H58" s="8"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="8" t="s">
         <v>3</v>
       </c>
@@ -2267,7 +2256,7 @@
       <c r="G59" s="8"/>
       <c r="H59" s="8"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="8" t="s">
         <v>5</v>
       </c>
@@ -2281,7 +2270,7 @@
       <c r="G60" s="8"/>
       <c r="H60" s="8"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="8" t="s">
         <v>6</v>
       </c>
@@ -2295,7 +2284,7 @@
       <c r="G61" s="8"/>
       <c r="H61" s="8"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="8" t="s">
         <v>8</v>
       </c>
@@ -2309,7 +2298,7 @@
       <c r="G62" s="8"/>
       <c r="H62" s="8"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>10</v>
       </c>
@@ -2321,7 +2310,7 @@
       <c r="G63" s="8"/>
       <c r="H63" s="8"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="8" t="s">
         <v>11</v>
       </c>
@@ -2347,7 +2336,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>74</v>
       </c>
@@ -2371,7 +2360,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>76</v>
       </c>
@@ -2395,7 +2384,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>61</v>
       </c>
@@ -2418,7 +2407,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>54</v>
       </c>
@@ -2441,7 +2430,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
       <c r="C69" s="3"/>
@@ -2451,7 +2440,7 @@
       <c r="G69" s="2"/>
       <c r="H69" s="2"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>0</v>
       </c>
@@ -2465,7 +2454,7 @@
       <c r="G70" s="8"/>
       <c r="H70" s="8"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
         <v>2</v>
       </c>
@@ -2479,7 +2468,7 @@
       <c r="G71" s="8"/>
       <c r="H71" s="8"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
         <v>3</v>
       </c>
@@ -2493,7 +2482,7 @@
       <c r="G72" s="8"/>
       <c r="H72" s="8"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
         <v>5</v>
       </c>
@@ -2507,7 +2496,7 @@
       <c r="G73" s="8"/>
       <c r="H73" s="8"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>6</v>
       </c>
@@ -2521,7 +2510,7 @@
       <c r="G74" s="8"/>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>8</v>
       </c>
@@ -2535,7 +2524,7 @@
       <c r="G75" s="8"/>
       <c r="H75" s="8"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>10</v>
       </c>
@@ -2547,7 +2536,7 @@
       <c r="G76" s="8"/>
       <c r="H76" s="8"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="8" t="s">
         <v>11</v>
       </c>
@@ -2573,7 +2562,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>77</v>
       </c>
@@ -2597,7 +2586,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>64</v>
       </c>
@@ -2621,7 +2610,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>79</v>
       </c>
@@ -2645,7 +2634,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>61</v>
       </c>
@@ -2668,7 +2657,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>54</v>
       </c>
@@ -2691,7 +2680,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="3"/>
@@ -2701,7 +2690,7 @@
       <c r="G83" s="2"/>
       <c r="H83" s="2"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>0</v>
       </c>
@@ -2715,7 +2704,7 @@
       <c r="G84" s="8"/>
       <c r="H84" s="8"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
         <v>2</v>
       </c>
@@ -2729,7 +2718,7 @@
       <c r="G85" s="8"/>
       <c r="H85" s="8"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="8" t="s">
         <v>3</v>
       </c>
@@ -2743,7 +2732,7 @@
       <c r="G86" s="8"/>
       <c r="H86" s="8"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
         <v>5</v>
       </c>
@@ -2757,7 +2746,7 @@
       <c r="G87" s="8"/>
       <c r="H87" s="8"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
         <v>6</v>
       </c>
@@ -2771,7 +2760,7 @@
       <c r="G88" s="8"/>
       <c r="H88" s="8"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
         <v>8</v>
       </c>
@@ -2785,7 +2774,7 @@
       <c r="G89" s="8"/>
       <c r="H89" s="8"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>10</v>
       </c>
@@ -2797,7 +2786,7 @@
       <c r="G90" s="8"/>
       <c r="H90" s="8"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
         <v>11</v>
       </c>
@@ -2823,7 +2812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>81</v>
       </c>
@@ -2847,7 +2836,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>76</v>
       </c>
@@ -2871,7 +2860,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>61</v>
       </c>
@@ -2894,7 +2883,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>54</v>
       </c>
@@ -2917,7 +2906,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="3"/>
@@ -2927,7 +2916,7 @@
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>0</v>
       </c>
@@ -2941,7 +2930,7 @@
       <c r="G97" s="8"/>
       <c r="H97" s="8"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="8" t="s">
         <v>2</v>
       </c>
@@ -2955,7 +2944,7 @@
       <c r="G98" s="8"/>
       <c r="H98" s="8"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="8" t="s">
         <v>3</v>
       </c>
@@ -2969,7 +2958,7 @@
       <c r="G99" s="8"/>
       <c r="H99" s="8"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="8" t="s">
         <v>5</v>
       </c>
@@ -2983,7 +2972,7 @@
       <c r="G100" s="8"/>
       <c r="H100" s="8"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="8" t="s">
         <v>6</v>
       </c>
@@ -2997,7 +2986,7 @@
       <c r="G101" s="8"/>
       <c r="H101" s="8"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="8" t="s">
         <v>8</v>
       </c>
@@ -3011,7 +3000,7 @@
       <c r="G102" s="8"/>
       <c r="H102" s="8"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>10</v>
       </c>
@@ -3023,7 +3012,7 @@
       <c r="G103" s="8"/>
       <c r="H103" s="8"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="8" t="s">
         <v>11</v>
       </c>
@@ -3049,7 +3038,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>169</v>
       </c>
@@ -3073,7 +3062,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>50</v>
       </c>
@@ -3097,7 +3086,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>55</v>
       </c>
@@ -3121,7 +3110,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>62</v>
       </c>
@@ -3145,7 +3134,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>70</v>
       </c>
@@ -3169,7 +3158,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>74</v>
       </c>
@@ -3193,7 +3182,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>77</v>
       </c>
@@ -3217,7 +3206,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>81</v>
       </c>
@@ -3241,7 +3230,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="3"/>
@@ -3251,7 +3240,7 @@
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>0</v>
       </c>
@@ -3265,7 +3254,7 @@
       <c r="G114" s="8"/>
       <c r="H114" s="8"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="8" t="s">
         <v>2</v>
       </c>
@@ -3279,7 +3268,7 @@
       <c r="G115" s="8"/>
       <c r="H115" s="8"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="8" t="s">
         <v>3</v>
       </c>
@@ -3293,7 +3282,7 @@
       <c r="G116" s="8"/>
       <c r="H116" s="8"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="8" t="s">
         <v>5</v>
       </c>
@@ -3307,7 +3296,7 @@
       <c r="G117" s="8"/>
       <c r="H117" s="8"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="8" t="s">
         <v>6</v>
       </c>
@@ -3321,7 +3310,7 @@
       <c r="G118" s="8"/>
       <c r="H118" s="8"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="8" t="s">
         <v>8</v>
       </c>
@@ -3335,7 +3324,7 @@
       <c r="G119" s="8"/>
       <c r="H119" s="8"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>10</v>
       </c>
@@ -3347,7 +3336,7 @@
       <c r="G120" s="8"/>
       <c r="H120" s="8"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="8" t="s">
         <v>11</v>
       </c>
@@ -3373,7 +3362,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>84</v>
       </c>
@@ -3397,7 +3386,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>87</v>
       </c>
@@ -3422,7 +3411,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>47</v>
       </c>
@@ -3447,7 +3436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>89</v>
       </c>
@@ -3472,7 +3461,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>91</v>
       </c>
@@ -3497,7 +3486,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>35</v>
       </c>
@@ -3518,7 +3507,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>93</v>
       </c>
@@ -3539,7 +3528,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>94</v>
       </c>
@@ -3563,7 +3552,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="3"/>
@@ -3573,7 +3562,7 @@
       <c r="G130" s="2"/>
       <c r="H130" s="2"/>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>0</v>
       </c>
@@ -3587,7 +3576,7 @@
       <c r="G131" s="8"/>
       <c r="H131" s="8"/>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A132" s="8" t="s">
         <v>2</v>
       </c>
@@ -3601,7 +3590,7 @@
       <c r="G132" s="8"/>
       <c r="H132" s="8"/>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A133" s="8" t="s">
         <v>3</v>
       </c>
@@ -3615,7 +3604,7 @@
       <c r="G133" s="8"/>
       <c r="H133" s="8"/>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A134" s="8" t="s">
         <v>5</v>
       </c>
@@ -3629,7 +3618,7 @@
       <c r="G134" s="8"/>
       <c r="H134" s="8"/>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A135" s="8" t="s">
         <v>6</v>
       </c>
@@ -3643,7 +3632,7 @@
       <c r="G135" s="8"/>
       <c r="H135" s="8"/>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A136" s="8" t="s">
         <v>8</v>
       </c>
@@ -3657,7 +3646,7 @@
       <c r="G136" s="8"/>
       <c r="H136" s="8"/>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>10</v>
       </c>
@@ -3669,7 +3658,7 @@
       <c r="G137" s="8"/>
       <c r="H137" s="8"/>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A138" s="8" t="s">
         <v>11</v>
       </c>
@@ -3695,7 +3684,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>96</v>
       </c>
@@ -3719,7 +3708,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>99</v>
       </c>
@@ -3740,7 +3729,7 @@
       </c>
       <c r="K140" s="14"/>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>37</v>
       </c>
@@ -3761,7 +3750,7 @@
       </c>
       <c r="K141" s="14"/>
     </row>
-    <row r="142" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>100</v>
       </c>
@@ -3782,7 +3771,7 @@
       </c>
       <c r="K142" s="14"/>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>101</v>
       </c>
@@ -3803,7 +3792,7 @@
       </c>
       <c r="K143" s="14"/>
     </row>
-    <row r="144" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>102</v>
       </c>
@@ -3824,7 +3813,7 @@
       </c>
       <c r="K144" s="14"/>
     </row>
-    <row r="145" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>103</v>
       </c>
@@ -3845,7 +3834,7 @@
       </c>
       <c r="K145" s="14"/>
     </row>
-    <row r="146" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>104</v>
       </c>
@@ -3866,7 +3855,7 @@
       </c>
       <c r="K146" s="14"/>
     </row>
-    <row r="147" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>105</v>
       </c>
@@ -3887,7 +3876,7 @@
       </c>
       <c r="K147" s="14"/>
     </row>
-    <row r="148" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>106</v>
       </c>
@@ -3908,7 +3897,7 @@
       </c>
       <c r="K148" s="14"/>
     </row>
-    <row r="149" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>107</v>
       </c>
@@ -3929,7 +3918,7 @@
       </c>
       <c r="K149" s="14"/>
     </row>
-    <row r="150" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>108</v>
       </c>
@@ -3950,7 +3939,7 @@
       </c>
       <c r="K150" s="14"/>
     </row>
-    <row r="151" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>109</v>
       </c>
@@ -3971,7 +3960,7 @@
       </c>
       <c r="K151" s="14"/>
     </row>
-    <row r="152" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>110</v>
       </c>
@@ -3992,7 +3981,7 @@
       </c>
       <c r="K152" s="14"/>
     </row>
-    <row r="153" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>111</v>
       </c>
@@ -4013,7 +4002,7 @@
       </c>
       <c r="K153" s="14"/>
     </row>
-    <row r="154" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>112</v>
       </c>
@@ -4034,7 +4023,7 @@
       </c>
       <c r="K154" s="14"/>
     </row>
-    <row r="155" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>113</v>
       </c>
@@ -4055,7 +4044,7 @@
       </c>
       <c r="K155" s="14"/>
     </row>
-    <row r="156" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>114</v>
       </c>
@@ -4076,7 +4065,7 @@
       </c>
       <c r="K156" s="14"/>
     </row>
-    <row r="157" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>115</v>
       </c>
@@ -4097,7 +4086,7 @@
       </c>
       <c r="K157" s="14"/>
     </row>
-    <row r="158" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>116</v>
       </c>
@@ -4118,7 +4107,7 @@
       </c>
       <c r="K158" s="14"/>
     </row>
-    <row r="159" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>117</v>
       </c>
@@ -4139,7 +4128,7 @@
       </c>
       <c r="K159" s="14"/>
     </row>
-    <row r="160" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="3"/>
@@ -4149,7 +4138,7 @@
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
     </row>
-    <row r="161" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>0</v>
       </c>
@@ -4164,7 +4153,7 @@
       <c r="H161" s="8"/>
       <c r="I161" s="8"/>
     </row>
-    <row r="162" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A162" s="8" t="s">
         <v>2</v>
       </c>
@@ -4179,7 +4168,7 @@
       <c r="H162" s="8"/>
       <c r="I162" s="8"/>
     </row>
-    <row r="163" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
         <v>3</v>
       </c>
@@ -4194,7 +4183,7 @@
       <c r="H163" s="8"/>
       <c r="I163" s="8"/>
     </row>
-    <row r="164" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A164" s="8" t="s">
         <v>5</v>
       </c>
@@ -4209,7 +4198,7 @@
       <c r="H164" s="8"/>
       <c r="I164" s="8"/>
     </row>
-    <row r="165" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A165" s="8" t="s">
         <v>6</v>
       </c>
@@ -4224,7 +4213,7 @@
       <c r="H165" s="8"/>
       <c r="I165" s="8"/>
     </row>
-    <row r="166" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A166" s="8" t="s">
         <v>8</v>
       </c>
@@ -4239,7 +4228,7 @@
       <c r="H166" s="8"/>
       <c r="I166" s="8"/>
     </row>
-    <row r="167" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>10</v>
       </c>
@@ -4252,7 +4241,7 @@
       <c r="H167" s="8"/>
       <c r="I167" s="8"/>
     </row>
-    <row r="168" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A168" s="8" t="s">
         <v>11</v>
       </c>
@@ -4279,7 +4268,7 @@
       </c>
       <c r="I168" s="8"/>
     </row>
-    <row r="169" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A169" s="8" t="s">
         <v>29</v>
       </c>
@@ -4302,7 +4291,7 @@
       <c r="H169" s="8"/>
       <c r="I169" s="8"/>
     </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A170" s="8" t="s">
         <v>123</v>
       </c>
@@ -4326,7 +4315,7 @@
       <c r="I170" s="8"/>
       <c r="K170" s="14"/>
     </row>
-    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A171" s="8" t="s">
         <v>126</v>
       </c>
@@ -4350,7 +4339,7 @@
       <c r="I171" s="8"/>
       <c r="K171" s="14"/>
     </row>
-    <row r="172" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A172" s="8" t="s">
         <v>128</v>
       </c>
@@ -4374,7 +4363,7 @@
       <c r="I172" s="8"/>
       <c r="K172" s="14"/>
     </row>
-    <row r="173" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A173" s="8" t="s">
         <v>130</v>
       </c>
@@ -4398,7 +4387,7 @@
       <c r="I173" s="8"/>
       <c r="K173" s="14"/>
     </row>
-    <row r="174" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A174" s="8" t="s">
         <v>121</v>
       </c>
@@ -4424,7 +4413,7 @@
       <c r="I174" s="8"/>
       <c r="K174" s="14"/>
     </row>
-    <row r="175" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A175" s="8" t="s">
         <v>131</v>
       </c>
@@ -4450,7 +4439,7 @@
       <c r="I175" s="8"/>
       <c r="K175" s="14"/>
     </row>
-    <row r="176" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A176" s="8" t="s">
         <v>133</v>
       </c>
@@ -4476,7 +4465,7 @@
       <c r="I176" s="8"/>
       <c r="K176" s="14"/>
     </row>
-    <row r="177" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A177" s="8" t="s">
         <v>135</v>
       </c>
@@ -4502,7 +4491,7 @@
       <c r="I177" s="8"/>
       <c r="K177" s="14"/>
     </row>
-    <row r="178" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A178" s="8" t="s">
         <v>137</v>
       </c>
@@ -4528,7 +4517,7 @@
       <c r="I178" s="8"/>
       <c r="K178" s="14"/>
     </row>
-    <row r="179" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A179" s="8" t="s">
         <v>138</v>
       </c>
@@ -4554,7 +4543,7 @@
       <c r="I179" s="8"/>
       <c r="K179" s="14"/>
     </row>
-    <row r="180" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A180" s="8" t="s">
         <v>139</v>
       </c>
@@ -4580,7 +4569,7 @@
       <c r="I180" s="8"/>
       <c r="K180" s="14"/>
     </row>
-    <row r="181" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A181" s="8" t="s">
         <v>142</v>
       </c>
@@ -4606,7 +4595,7 @@
       <c r="I181" s="8"/>
       <c r="K181" s="14"/>
     </row>
-    <row r="182" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A182" s="8" t="s">
         <v>145</v>
       </c>
@@ -4632,7 +4621,7 @@
       <c r="I182" s="8"/>
       <c r="K182" s="14"/>
     </row>
-    <row r="183" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A183" s="8" t="s">
         <v>147</v>
       </c>
@@ -4658,7 +4647,7 @@
       <c r="I183" s="8"/>
       <c r="K183" s="14"/>
     </row>
-    <row r="184" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A184" s="8" t="s">
         <v>149</v>
       </c>
@@ -4684,7 +4673,7 @@
       <c r="I184" s="8"/>
       <c r="K184" s="14"/>
     </row>
-    <row r="185" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A185" s="8" t="s">
         <v>151</v>
       </c>
@@ -4710,7 +4699,7 @@
       <c r="I185" s="8"/>
       <c r="K185" s="14"/>
     </row>
-    <row r="186" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A186" s="8" t="s">
         <v>153</v>
       </c>
@@ -4736,7 +4725,7 @@
       <c r="I186" s="8"/>
       <c r="K186" s="14"/>
     </row>
-    <row r="187" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="3"/>
@@ -4747,7 +4736,7 @@
       <c r="H187" s="2"/>
       <c r="K187" s="14"/>
     </row>
-    <row r="188" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>0</v>
       </c>
@@ -4762,7 +4751,7 @@
       <c r="H188" s="8"/>
       <c r="K188" s="14"/>
     </row>
-    <row r="189" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A189" s="8" t="s">
         <v>2</v>
       </c>
@@ -4777,7 +4766,7 @@
       <c r="H189" s="8"/>
       <c r="K189" s="14"/>
     </row>
-    <row r="190" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A190" s="8" t="s">
         <v>3</v>
       </c>
@@ -4791,7 +4780,7 @@
       <c r="G190" s="8"/>
       <c r="H190" s="8"/>
     </row>
-    <row r="191" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A191" s="8" t="s">
         <v>5</v>
       </c>
@@ -4805,7 +4794,7 @@
       <c r="G191" s="8"/>
       <c r="H191" s="8"/>
     </row>
-    <row r="192" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A192" s="8" t="s">
         <v>6</v>
       </c>
@@ -4819,7 +4808,7 @@
       <c r="G192" s="8"/>
       <c r="H192" s="8"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A193" s="8" t="s">
         <v>8</v>
       </c>
@@ -4833,7 +4822,7 @@
       <c r="G193" s="8"/>
       <c r="H193" s="8"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>10</v>
       </c>
@@ -4845,7 +4834,7 @@
       <c r="G194" s="8"/>
       <c r="H194" s="8"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A195" s="8" t="s">
         <v>11</v>
       </c>
@@ -4871,7 +4860,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="8" t="s">
         <v>120</v>
       </c>
@@ -4895,7 +4884,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A197" s="8" t="s">
         <v>121</v>
       </c>
@@ -4919,7 +4908,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>54</v>
       </c>
@@ -4943,7 +4932,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>29</v>
       </c>
@@ -4966,7 +4955,7 @@
       </c>
       <c r="H199" s="8"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="3"/>
@@ -4976,7 +4965,7 @@
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>0</v>
       </c>
@@ -4990,7 +4979,7 @@
       <c r="G201" s="8"/>
       <c r="H201" s="8"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A202" s="8" t="s">
         <v>2</v>
       </c>
@@ -5004,7 +4993,7 @@
       <c r="G202" s="8"/>
       <c r="H202" s="8"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A203" s="8" t="s">
         <v>3</v>
       </c>
@@ -5018,7 +5007,7 @@
       <c r="G203" s="8"/>
       <c r="H203" s="8"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A204" s="8" t="s">
         <v>5</v>
       </c>
@@ -5032,7 +5021,7 @@
       <c r="G204" s="8"/>
       <c r="H204" s="8"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A205" s="8" t="s">
         <v>6</v>
       </c>
@@ -5046,7 +5035,7 @@
       <c r="G205" s="8"/>
       <c r="H205" s="8"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A206" s="8" t="s">
         <v>8</v>
       </c>
@@ -5060,7 +5049,7 @@
       <c r="G206" s="8"/>
       <c r="H206" s="8"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>10</v>
       </c>
@@ -5072,7 +5061,7 @@
       <c r="G207" s="8"/>
       <c r="H207" s="8"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A208" s="8" t="s">
         <v>11</v>
       </c>
@@ -5098,7 +5087,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A209" s="8" t="s">
         <v>157</v>
       </c>
@@ -5122,7 +5111,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A210" s="8" t="s">
         <v>121</v>
       </c>
@@ -5146,7 +5135,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>54</v>
       </c>
@@ -5170,7 +5159,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>29</v>
       </c>
@@ -5193,7 +5182,7 @@
       </c>
       <c r="H212" s="8"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="3"/>
@@ -5203,7 +5192,7 @@
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>0</v>
       </c>
@@ -5217,7 +5206,7 @@
       <c r="G214" s="8"/>
       <c r="H214" s="8"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A215" s="8" t="s">
         <v>2</v>
       </c>
@@ -5231,7 +5220,7 @@
       <c r="G215" s="8"/>
       <c r="H215" s="8"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A216" s="8" t="s">
         <v>3</v>
       </c>
@@ -5245,7 +5234,7 @@
       <c r="G216" s="8"/>
       <c r="H216" s="8"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A217" s="8" t="s">
         <v>5</v>
       </c>
@@ -5259,7 +5248,7 @@
       <c r="G217" s="8"/>
       <c r="H217" s="8"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A218" s="8" t="s">
         <v>6</v>
       </c>
@@ -5273,7 +5262,7 @@
       <c r="G218" s="8"/>
       <c r="H218" s="8"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A219" s="8" t="s">
         <v>8</v>
       </c>
@@ -5287,7 +5276,7 @@
       <c r="G219" s="8"/>
       <c r="H219" s="8"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>10</v>
       </c>
@@ -5299,7 +5288,7 @@
       <c r="G220" s="8"/>
       <c r="H220" s="8"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A221" s="8" t="s">
         <v>11</v>
       </c>
@@ -5325,7 +5314,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A222" s="8" t="s">
         <v>160</v>
       </c>
@@ -5349,7 +5338,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>84</v>
       </c>
@@ -5373,7 +5362,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A224" s="8" t="s">
         <v>157</v>
       </c>
@@ -5397,7 +5386,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A225" s="8" t="s">
         <v>162</v>
       </c>
@@ -5421,7 +5410,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="8" t="s">
         <v>158</v>
       </c>
@@ -5445,7 +5434,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>29</v>
       </c>
@@ -5467,7 +5456,7 @@
       </c>
       <c r="H227" s="8"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="3"/>
@@ -5477,7 +5466,7 @@
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>0</v>
       </c>
@@ -5491,7 +5480,7 @@
       <c r="G229" s="8"/>
       <c r="H229" s="8"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A230" s="8" t="s">
         <v>2</v>
       </c>
@@ -5505,7 +5494,7 @@
       <c r="G230" s="8"/>
       <c r="H230" s="8"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A231" s="8" t="s">
         <v>3</v>
       </c>
@@ -5519,7 +5508,7 @@
       <c r="G231" s="8"/>
       <c r="H231" s="8"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A232" s="8" t="s">
         <v>5</v>
       </c>
@@ -5533,7 +5522,7 @@
       <c r="G232" s="8"/>
       <c r="H232" s="8"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A233" s="8" t="s">
         <v>6</v>
       </c>
@@ -5547,7 +5536,7 @@
       <c r="G233" s="8"/>
       <c r="H233" s="8"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A234" s="8" t="s">
         <v>8</v>
       </c>
@@ -5561,7 +5550,7 @@
       <c r="G234" s="8"/>
       <c r="H234" s="8"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>10</v>
       </c>
@@ -5573,7 +5562,7 @@
       <c r="G235" s="8"/>
       <c r="H235" s="8"/>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A236" s="8" t="s">
         <v>11</v>
       </c>
@@ -5599,7 +5588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A237" s="8" t="s">
         <v>158</v>
       </c>
@@ -5623,7 +5612,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>84</v>
       </c>
@@ -5647,7 +5636,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A239" s="8" t="s">
         <v>157</v>
       </c>
@@ -5671,7 +5660,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>54</v>
       </c>
@@ -5694,7 +5683,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A241" s="8" t="s">
         <v>160</v>
       </c>
@@ -5718,7 +5707,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>29</v>
       </c>
@@ -5740,7 +5729,7 @@
       </c>
       <c r="H242" s="8"/>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="3"/>
@@ -5750,7 +5739,7 @@
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>0</v>
       </c>
@@ -5764,7 +5753,7 @@
       <c r="G244" s="8"/>
       <c r="H244" s="8"/>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A245" s="8" t="s">
         <v>2</v>
       </c>
@@ -5778,7 +5767,7 @@
       <c r="G245" s="8"/>
       <c r="H245" s="8"/>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A246" s="8" t="s">
         <v>3</v>
       </c>
@@ -5792,7 +5781,7 @@
       <c r="G246" s="8"/>
       <c r="H246" s="8"/>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A247" s="8" t="s">
         <v>5</v>
       </c>
@@ -5806,7 +5795,7 @@
       <c r="G247" s="8"/>
       <c r="H247" s="8"/>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A248" s="8" t="s">
         <v>6</v>
       </c>
@@ -5820,7 +5809,7 @@
       <c r="G248" s="8"/>
       <c r="H248" s="8"/>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A249" s="8" t="s">
         <v>8</v>
       </c>
@@ -5834,7 +5823,7 @@
       <c r="G249" s="8"/>
       <c r="H249" s="8"/>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>10</v>
       </c>
@@ -5846,7 +5835,7 @@
       <c r="G250" s="8"/>
       <c r="H250" s="8"/>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A251" s="8" t="s">
         <v>11</v>
       </c>
@@ -5872,7 +5861,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A252" s="8" t="s">
         <v>40</v>
       </c>
@@ -5896,7 +5885,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
         <v>167</v>
       </c>
@@ -5920,7 +5909,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A254" s="7" t="s">
         <v>32</v>
       </c>
@@ -5942,7 +5931,7 @@
       </c>
       <c r="H254" s="8"/>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
         <v>38</v>
       </c>
@@ -5965,7 +5954,7 @@
       </c>
       <c r="H255" s="8"/>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="3"/>
@@ -5975,7 +5964,7 @@
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A257" s="19" t="s">
         <v>0</v>
       </c>
@@ -5989,7 +5978,7 @@
       <c r="G257" s="5"/>
       <c r="H257" s="5"/>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A258" s="19" t="s">
         <v>2</v>
       </c>
@@ -6003,7 +5992,7 @@
       <c r="G258" s="5"/>
       <c r="H258" s="5"/>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A259" s="19" t="s">
         <v>3</v>
       </c>
@@ -6017,7 +6006,7 @@
       <c r="G259" s="5"/>
       <c r="H259" s="5"/>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>6</v>
       </c>
@@ -6031,7 +6020,7 @@
       <c r="G260" s="5"/>
       <c r="H260" s="5"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A261" s="19" t="s">
         <v>5</v>
       </c>
@@ -6045,7 +6034,7 @@
       <c r="G261" s="5"/>
       <c r="H261" s="5"/>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A262" s="19" t="s">
         <v>8</v>
       </c>
@@ -6059,7 +6048,7 @@
       <c r="G262" s="5"/>
       <c r="H262" s="5"/>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="19" t="s">
         <v>200</v>
       </c>
@@ -6071,7 +6060,7 @@
       <c r="G263" s="5"/>
       <c r="H263" s="5"/>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A264" s="19" t="s">
         <v>10</v>
       </c>
@@ -6083,7 +6072,7 @@
       <c r="G264" s="5"/>
       <c r="H264" s="5"/>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
         <v>11</v>
       </c>
@@ -6109,7 +6098,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A266" s="17" t="s">
         <v>184</v>
       </c>
@@ -6133,7 +6122,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>46</v>
       </c>
@@ -6157,7 +6146,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A268" s="17" t="s">
         <v>201</v>
       </c>
@@ -6181,7 +6170,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A269" s="17" t="s">
         <v>203</v>
       </c>
@@ -6205,7 +6194,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A270" s="17" t="s">
         <v>205</v>
       </c>
@@ -6229,7 +6218,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>29</v>
       </c>
@@ -6250,7 +6239,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>100</v>
       </c>
@@ -6271,7 +6260,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>99</v>
       </c>
@@ -6292,7 +6281,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" s="18" t="s">
         <v>206</v>
       </c>
@@ -6313,7 +6302,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>37</v>
       </c>
@@ -6334,7 +6323,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="18" t="s">
         <v>194</v>
       </c>
@@ -6355,7 +6344,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" s="18" t="s">
         <v>104</v>
       </c>
@@ -6376,7 +6365,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="18" t="s">
         <v>207</v>
       </c>
@@ -6397,7 +6386,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="18" t="s">
         <v>208</v>
       </c>
@@ -6418,7 +6407,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="18" t="s">
         <v>209</v>
       </c>
@@ -6439,7 +6428,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A281" s="18" t="s">
         <v>114</v>
       </c>
@@ -6460,7 +6449,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="18" t="s">
         <v>210</v>
       </c>
@@ -6481,7 +6470,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A283" s="18" t="s">
         <v>211</v>
       </c>
@@ -6501,7 +6490,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A284" s="18" t="s">
         <v>195</v>
       </c>
@@ -6521,7 +6510,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="18" t="s">
         <v>107</v>
       </c>
@@ -6541,7 +6530,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="18" t="s">
         <v>212</v>
       </c>
@@ -6561,7 +6550,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="18" t="s">
         <v>213</v>
       </c>
@@ -6581,7 +6570,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="18" t="s">
         <v>214</v>
       </c>
@@ -6601,7 +6590,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A289" s="18" t="s">
         <v>215</v>
       </c>
@@ -6621,7 +6610,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A290" s="18" t="s">
         <v>216</v>
       </c>
@@ -6641,7 +6630,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="3"/>
@@ -6651,7 +6640,7 @@
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
     </row>
-    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A292" s="19" t="s">
         <v>0</v>
       </c>
@@ -6665,7 +6654,7 @@
       <c r="G292" s="5"/>
       <c r="H292" s="5"/>
     </row>
-    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A293" s="19" t="s">
         <v>2</v>
       </c>
@@ -6679,7 +6668,7 @@
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
     </row>
-    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A294" s="19" t="s">
         <v>3</v>
       </c>
@@ -6693,7 +6682,7 @@
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
     </row>
-    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>6</v>
       </c>
@@ -6707,7 +6696,7 @@
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
     </row>
-    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A296" s="19" t="s">
         <v>5</v>
       </c>
@@ -6721,7 +6710,7 @@
       <c r="G296" s="5"/>
       <c r="H296" s="5"/>
     </row>
-    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A297" s="19" t="s">
         <v>8</v>
       </c>
@@ -6735,7 +6724,7 @@
       <c r="G297" s="5"/>
       <c r="H297" s="5"/>
     </row>
-    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A298" s="19" t="s">
         <v>10</v>
       </c>
@@ -6747,7 +6736,7 @@
       <c r="G298" s="5"/>
       <c r="H298" s="5"/>
     </row>
-    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="s">
         <v>11</v>
       </c>
@@ -6773,7 +6762,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A300" s="17" t="s">
         <v>205</v>
       </c>
@@ -6797,7 +6786,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>54</v>
       </c>
@@ -6821,7 +6810,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>224</v>
       </c>
@@ -6844,7 +6833,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>226</v>
       </c>
@@ -6867,7 +6856,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>228</v>
       </c>
@@ -6890,7 +6879,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>230</v>
       </c>
@@ -6913,7 +6902,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>232</v>
       </c>
@@ -6936,7 +6925,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>87</v>
       </c>
@@ -6959,7 +6948,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>234</v>
       </c>
@@ -6982,7 +6971,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>89</v>
       </c>
@@ -7005,7 +6994,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>94</v>
       </c>
@@ -7037,17 +7026,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD968991-55C9-4627-9323-29F50518FFEB}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7061,7 +7050,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -7075,7 +7064,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -7089,7 +7078,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -7103,7 +7092,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -7117,7 +7106,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -7131,7 +7120,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -7143,7 +7132,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -7169,7 +7158,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1</v>
       </c>
@@ -7193,7 +7182,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -7217,7 +7206,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -7241,7 +7230,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -7264,7 +7253,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>179</v>
       </c>
@@ -7288,7 +7277,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>238</v>
       </c>
@@ -7311,7 +7300,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>239</v>
       </c>
@@ -7335,7 +7324,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>27</v>
       </c>
@@ -7358,7 +7347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="14" t="s">
         <v>241</v>
       </c>
@@ -7381,7 +7370,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>37</v>
       </c>
@@ -7401,7 +7390,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>38</v>
       </c>
@@ -7421,7 +7410,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>36</v>
       </c>
@@ -7442,7 +7431,7 @@
       </c>
       <c r="H20" s="14"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -7463,7 +7452,7 @@
       </c>
       <c r="H21" s="14"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
@@ -7483,7 +7472,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>32</v>
       </c>
@@ -7503,7 +7492,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="3"/>
@@ -7513,7 +7502,7 @@
       <c r="G24" s="2"/>
       <c r="H24" s="2"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>0</v>
       </c>
@@ -7527,7 +7516,7 @@
       <c r="G25" s="8"/>
       <c r="H25" s="8"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
         <v>2</v>
       </c>
@@ -7541,7 +7530,7 @@
       <c r="G26" s="8"/>
       <c r="H26" s="8"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>3</v>
       </c>
@@ -7555,7 +7544,7 @@
       <c r="G27" s="8"/>
       <c r="H27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>5</v>
       </c>
@@ -7569,7 +7558,7 @@
       <c r="G28" s="8"/>
       <c r="H28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>6</v>
       </c>
@@ -7583,7 +7572,7 @@
       <c r="G29" s="8"/>
       <c r="H29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
         <v>8</v>
       </c>
@@ -7597,7 +7586,7 @@
       <c r="G30" s="8"/>
       <c r="H30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -7609,7 +7598,7 @@
       <c r="G31" s="8"/>
       <c r="H31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
         <v>11</v>
       </c>
@@ -7635,7 +7624,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -7659,7 +7648,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>46</v>
       </c>
@@ -7683,7 +7672,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="17" t="s">
         <v>184</v>
       </c>
@@ -7707,7 +7696,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>54</v>
       </c>
@@ -7730,7 +7719,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>179</v>
       </c>
@@ -7754,7 +7743,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>238</v>
       </c>
@@ -7777,7 +7766,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>239</v>
       </c>
@@ -7801,7 +7790,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>27</v>
       </c>
@@ -7824,7 +7813,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>241</v>
       </c>
@@ -7847,7 +7836,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>37</v>
       </c>
@@ -7867,7 +7856,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>38</v>
       </c>
@@ -7887,7 +7876,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>36</v>
       </c>
@@ -7908,7 +7897,7 @@
       </c>
       <c r="H44" s="14"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>29</v>
       </c>
@@ -7929,7 +7918,7 @@
       </c>
       <c r="H45" s="14"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>38</v>
       </c>
@@ -7949,7 +7938,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>32</v>
       </c>
@@ -7969,7 +7958,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
       <c r="C48" s="3"/>
@@ -7979,7 +7968,7 @@
       <c r="G48" s="2"/>
       <c r="H48" s="2"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>0</v>
       </c>
@@ -7993,7 +7982,7 @@
       <c r="G49" s="8"/>
       <c r="H49" s="8"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>2</v>
       </c>
@@ -8007,7 +7996,7 @@
       <c r="G50" s="8"/>
       <c r="H50" s="8"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>3</v>
       </c>
@@ -8021,7 +8010,7 @@
       <c r="G51" s="8"/>
       <c r="H51" s="8"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
         <v>5</v>
       </c>
@@ -8035,7 +8024,7 @@
       <c r="G52" s="8"/>
       <c r="H52" s="8"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
         <v>6</v>
       </c>
@@ -8049,7 +8038,7 @@
       <c r="G53" s="8"/>
       <c r="H53" s="8"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="8" t="s">
         <v>8</v>
       </c>
@@ -8063,7 +8052,7 @@
       <c r="G54" s="8"/>
       <c r="H54" s="8"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>10</v>
       </c>
@@ -8075,7 +8064,7 @@
       <c r="G55" s="8"/>
       <c r="H55" s="8"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="8" t="s">
         <v>11</v>
       </c>
@@ -8101,7 +8090,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>170</v>
       </c>
@@ -8125,7 +8114,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="8" t="s">
         <v>40</v>
       </c>
@@ -8149,7 +8138,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>77</v>
       </c>
@@ -8173,7 +8162,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>27</v>
       </c>
@@ -8197,7 +8186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>32</v>
       </c>
@@ -8217,7 +8206,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>54</v>
       </c>
@@ -8240,7 +8229,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>34</v>
       </c>
@@ -8260,7 +8249,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>35</v>
       </c>
@@ -8280,7 +8269,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>37</v>
       </c>
@@ -8300,7 +8289,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>38</v>
       </c>
@@ -8321,7 +8310,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>38</v>
       </c>
@@ -8342,7 +8331,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="8" t="s">
         <v>153</v>
       </c>
@@ -8365,40 +8354,40 @@
         <v>154</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B69" s="15"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B70" s="15"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B71" s="15"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B72" s="15"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B73" s="4"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B74" s="15"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B75" s="15"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B76" s="15"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B77" s="15"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B78" s="15"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B79" s="15"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="8"/>
       <c r="B80" s="13"/>
       <c r="C80" s="8"/>
@@ -8416,17 +8405,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20D067F8-C305-44D3-8E28-CF1FDCAD7A72}">
   <dimension ref="A1:H75"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="86.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="86.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="33.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8440,7 +8429,7 @@
       <c r="G1" s="8"/>
       <c r="H1" s="8"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>2</v>
       </c>
@@ -8454,7 +8443,7 @@
       <c r="G2" s="8"/>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>3</v>
       </c>
@@ -8468,7 +8457,7 @@
       <c r="G3" s="8"/>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>5</v>
       </c>
@@ -8482,7 +8471,7 @@
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>6</v>
       </c>
@@ -8496,7 +8485,7 @@
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>8</v>
       </c>
@@ -8510,7 +8499,7 @@
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -8522,7 +8511,7 @@
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>11</v>
       </c>
@@ -8548,7 +8537,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>171</v>
       </c>
@@ -8572,7 +8561,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>46</v>
       </c>
@@ -8596,7 +8585,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>162</v>
       </c>
@@ -8620,7 +8609,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>54</v>
       </c>
@@ -8643,7 +8632,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>175</v>
       </c>
@@ -8667,7 +8656,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>177</v>
       </c>
@@ -8691,7 +8680,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -8715,7 +8704,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>179</v>
       </c>
@@ -8739,7 +8728,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>48</v>
       </c>
@@ -8763,7 +8752,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>180</v>
       </c>
@@ -8788,7 +8777,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>181</v>
       </c>
@@ -8811,7 +8800,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -8831,7 +8820,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -8851,7 +8840,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>187</v>
       </c>
@@ -8871,7 +8860,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>37</v>
       </c>
@@ -8891,7 +8880,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -8911,7 +8900,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>188</v>
       </c>
@@ -8931,7 +8920,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>189</v>
       </c>
@@ -8951,7 +8940,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>190</v>
       </c>
@@ -8971,7 +8960,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>191</v>
       </c>
@@ -8991,7 +8980,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>189</v>
       </c>
@@ -9011,7 +9000,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -9031,7 +9020,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>192</v>
       </c>
@@ -9051,7 +9040,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>193</v>
       </c>
@@ -9071,7 +9060,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>194</v>
       </c>
@@ -9091,7 +9080,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>195</v>
       </c>
@@ -9111,7 +9100,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>196</v>
       </c>
@@ -9131,7 +9120,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="8" t="s">
         <v>197</v>
       </c>
@@ -9152,7 +9141,7 @@
       </c>
       <c r="H36" s="8"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="8" t="s">
         <v>198</v>
       </c>
@@ -9174,7 +9163,7 @@
       </c>
       <c r="H37" s="8"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="3"/>
@@ -9184,7 +9173,7 @@
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>0</v>
       </c>
@@ -9198,7 +9187,7 @@
       <c r="G39" s="8"/>
       <c r="H39" s="8"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
         <v>2</v>
       </c>
@@ -9212,7 +9201,7 @@
       <c r="G40" s="8"/>
       <c r="H40" s="8"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
         <v>3</v>
       </c>
@@ -9226,7 +9215,7 @@
       <c r="G41" s="8"/>
       <c r="H41" s="8"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
         <v>5</v>
       </c>
@@ -9240,7 +9229,7 @@
       <c r="G42" s="8"/>
       <c r="H42" s="8"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
         <v>6</v>
       </c>
@@ -9254,7 +9243,7 @@
       <c r="G43" s="8"/>
       <c r="H43" s="8"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
         <v>8</v>
       </c>
@@ -9268,7 +9257,7 @@
       <c r="G44" s="8"/>
       <c r="H44" s="8"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>10</v>
       </c>
@@ -9280,7 +9269,7 @@
       <c r="G45" s="8"/>
       <c r="H45" s="8"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>11</v>
       </c>
@@ -9306,7 +9295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>174</v>
       </c>
@@ -9330,7 +9319,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -9354,7 +9343,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="17" t="s">
         <v>184</v>
       </c>
@@ -9378,7 +9367,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>54</v>
       </c>
@@ -9401,7 +9390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>175</v>
       </c>
@@ -9425,7 +9414,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>177</v>
       </c>
@@ -9449,7 +9438,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>72</v>
       </c>
@@ -9473,7 +9462,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>179</v>
       </c>
@@ -9497,7 +9486,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>48</v>
       </c>
@@ -9521,7 +9510,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>180</v>
       </c>
@@ -9546,7 +9535,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>181</v>
       </c>
@@ -9569,7 +9558,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>99</v>
       </c>
@@ -9589,7 +9578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -9609,7 +9598,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>187</v>
       </c>
@@ -9629,7 +9618,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>37</v>
       </c>
@@ -9649,7 +9638,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>38</v>
       </c>
@@ -9669,7 +9658,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>188</v>
       </c>
@@ -9689,7 +9678,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>189</v>
       </c>
@@ -9709,7 +9698,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>190</v>
       </c>
@@ -9729,7 +9718,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>191</v>
       </c>
@@ -9749,7 +9738,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>189</v>
       </c>
@@ -9769,7 +9758,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>38</v>
       </c>
@@ -9789,7 +9778,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>192</v>
       </c>
@@ -9809,7 +9798,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>193</v>
       </c>
@@ -9829,7 +9818,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>194</v>
       </c>
@@ -9849,7 +9838,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>195</v>
       </c>
@@ -9869,7 +9858,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>196</v>
       </c>
@@ -9889,7 +9878,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="8" t="s">
         <v>197</v>
       </c>
@@ -9910,7 +9899,7 @@
       </c>
       <c r="H74" s="8"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
         <v>198</v>
       </c>
@@ -9941,18 +9930,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{998EBEEB-B02A-47FC-B25F-8D09BAB943A0}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9960,7 +9949,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -9968,7 +9957,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -9976,7 +9965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -9984,7 +9973,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -9992,7 +9981,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -10000,12 +9989,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -10031,7 +10020,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>223</v>
       </c>
@@ -10054,7 +10043,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>171</v>
       </c>
@@ -10077,7 +10066,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>54</v>
       </c>
@@ -10101,7 +10090,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -10123,7 +10112,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>220</v>
       </c>
@@ -10146,7 +10135,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>87</v>
       </c>
@@ -10169,7 +10158,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>29</v>
       </c>
@@ -10189,7 +10178,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>38</v>
       </c>
@@ -10209,7 +10198,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>222</v>
       </c>
@@ -10232,7 +10221,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>93</v>
       </c>
